--- a/功能需求.xlsx
+++ b/功能需求.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
   <si>
     <t>一、需求数据</t>
   </si>
@@ -215,6 +215,78 @@
   </si>
   <si>
     <t>没有翻页按钮</t>
+  </si>
+  <si>
+    <t>软件给PLC</t>
+  </si>
+  <si>
+    <t>PLC给软件</t>
+  </si>
+  <si>
+    <t>软件准备好</t>
+  </si>
+  <si>
+    <t>D622</t>
+  </si>
+  <si>
+    <t>软件给PLC的准备好(长度1个字，INT=1为准备好)</t>
+  </si>
+  <si>
+    <t>给定文件名称(长度20个字)</t>
+  </si>
+  <si>
+    <t>D600</t>
+  </si>
+  <si>
+    <t>PLC给软件的文件名（长度20个字，字符串（支持中文））</t>
+  </si>
+  <si>
+    <t>识图进行中</t>
+  </si>
+  <si>
+    <t>操作导入图纸</t>
+  </si>
+  <si>
+    <t>给定识图边界</t>
+  </si>
+  <si>
+    <t>D620</t>
+  </si>
+  <si>
+    <t>PLC给软件的识图界限(长度2个字，REAL)</t>
+  </si>
+  <si>
+    <t>操作一键识别匹配</t>
+  </si>
+  <si>
+    <t>操作导出数据</t>
+  </si>
+  <si>
+    <t>操作数据发送</t>
+  </si>
+  <si>
+    <t>给出导出成功或者导出失败</t>
+  </si>
+  <si>
+    <t>D623</t>
+  </si>
+  <si>
+    <t>软件给PLC的识图结果（成功或者失败）（长度1个字，INT =1成功 =2失败 =3未找到)</t>
+  </si>
+  <si>
+    <t>关闭识图进行中</t>
+  </si>
+  <si>
+    <t>D624</t>
+  </si>
+  <si>
+    <t>软件给PLC的识图进行中(长度1个字，INT =1为进行中)</t>
+  </si>
+  <si>
+    <t>D625</t>
+  </si>
+  <si>
+    <t>软件状态 INT =1 存活PLC往里写0</t>
   </si>
 </sst>
 </file>
@@ -227,9 +299,15 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -385,7 +463,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -395,6 +473,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -771,16 +855,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -789,37 +870,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -834,75 +915,93 @@
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1288,7 +1387,7 @@
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
       <tableStyleElement type="secondColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="TableStylePreset8_Accent1 1" pivot="0" count="7" xr9:uid="{E00E9FD5-82D0-40E2-BE6B-1E445809DE57}">
+    <tableStyle name="TableStylePreset8_Accent1 1" pivot="0" count="7" xr9:uid="{FFCEF0E9-7521-4F4D-A1E1-A38F92CC5649}">
       <tableStyleElement type="wholeTable" dxfId="15"/>
       <tableStyleElement type="headerRow" dxfId="14"/>
       <tableStyleElement type="totalRow" dxfId="13"/>
@@ -1312,8 +1411,8 @@
   </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="00000000"/>
       <color rgb="00FFFF00"/>
-      <color rgb="00000000"/>
     </mruColors>
   </colors>
   <extLst>
@@ -1666,551 +1765,551 @@
   <dimension ref="A1:H57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="6" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="19.3" customWidth="1"/>
-    <col min="4" max="4" width="11.3" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="7" width="42.2" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.3" style="6" customWidth="1"/>
+    <col min="5" max="5" width="10" style="6" customWidth="1"/>
+    <col min="6" max="7" width="42.2" style="6" customWidth="1"/>
     <col min="8" max="8" width="19.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="31.2" spans="1:8">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="7"/>
+    </row>
+    <row r="3" s="6" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A3" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="10" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="4">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="9">
         <v>20</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="9">
         <v>0</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="8"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="4">
+      <c r="A5" s="9">
         <v>2</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5" s="9">
         <v>1</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="9">
         <v>20</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="F5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="8"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="4">
+      <c r="A6" s="9">
         <v>3</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="9">
         <v>1</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="9">
         <v>21</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="8"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="4">
+      <c r="A7" s="9">
         <v>4</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7" s="9">
         <v>22</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="8"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="4">
+      <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="9">
         <v>1</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="9">
         <v>23</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="4"/>
-      <c r="H8" s="8"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="4">
+      <c r="A9" s="9">
         <v>6</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="4">
+      <c r="D9" s="9">
         <v>1</v>
       </c>
-      <c r="E9" s="4">
+      <c r="E9" s="9">
         <v>24</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="F9" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="4"/>
-      <c r="H9" s="8"/>
+      <c r="G9" s="9"/>
+      <c r="H9" s="13"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="4">
+      <c r="A10" s="9">
         <v>7</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="9">
         <v>1</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="9">
         <v>25</v>
       </c>
-      <c r="F10" s="9" t="s">
+      <c r="F10" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="4"/>
-      <c r="H10" s="8"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="4">
+      <c r="A11" s="9">
         <v>8</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="4">
+      <c r="D11" s="9">
         <v>1</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="9">
         <v>26</v>
       </c>
-      <c r="F11" s="9" t="s">
+      <c r="F11" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="4"/>
-      <c r="H11" s="8"/>
+      <c r="G11" s="9"/>
+      <c r="H11" s="13"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="4">
+      <c r="A12" s="9">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="4">
+      <c r="D12" s="9">
         <v>1</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="9">
         <v>27</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="4"/>
-      <c r="H12" s="8"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="4">
+      <c r="A13" s="9">
         <v>10</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="4">
+      <c r="D13" s="9">
         <v>1</v>
       </c>
-      <c r="E13" s="4">
+      <c r="E13" s="9">
         <v>28</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="8"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="13"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="4">
+      <c r="A14" s="9">
         <v>11</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="4">
+      <c r="D14" s="9">
         <v>1</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="9">
         <v>29</v>
       </c>
-      <c r="F14" s="9" t="s">
+      <c r="F14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="8"/>
+      <c r="G14" s="9"/>
+      <c r="H14" s="13"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="4">
+      <c r="A15" s="9">
         <v>12</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D15" s="9">
         <v>2</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="9">
         <v>30</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="8"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="13"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="4">
+      <c r="A16" s="9">
         <v>13</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="4">
+      <c r="D16" s="9">
         <v>2</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="9">
         <v>32</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="8"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="13"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="4">
+      <c r="A17" s="9">
         <v>14</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17" s="9">
         <v>2</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17" s="9">
         <v>32</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="F17" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="8"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="4">
+      <c r="A18" s="9">
         <v>15</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="4">
+      <c r="D18" s="9">
         <v>2</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="9">
         <v>34</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="F18" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="8"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="4">
+      <c r="A19" s="9">
         <v>16</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="9">
         <v>2</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="9">
         <v>38</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="F19" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="8"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="13"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:8">
-      <c r="A20" s="4">
+      <c r="A20" s="9">
         <v>17</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="4">
+      <c r="D20" s="9">
         <v>320</v>
       </c>
-      <c r="E20" s="4">
+      <c r="E20" s="9">
         <v>40</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="10" t="s">
+      <c r="G20" s="9"/>
+      <c r="H20" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="4">
+      <c r="A21" s="9">
         <v>19</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="4">
+      <c r="D21" s="9">
         <v>80</v>
       </c>
-      <c r="E21" s="4">
+      <c r="E21" s="9">
         <v>360</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="10"/>
+      <c r="H21" s="15"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="4">
+      <c r="A22" s="9">
         <v>20</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="4">
+      <c r="D22" s="9">
         <v>80</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="9">
         <v>440</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="10"/>
+      <c r="H22" s="15"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:8">
-      <c r="A23" s="4">
+      <c r="A23" s="9">
         <v>21</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="4">
+      <c r="D23" s="9">
         <v>320</v>
       </c>
-      <c r="E23" s="4">
+      <c r="E23" s="9">
         <v>520</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="10" t="s">
+      <c r="G23" s="9"/>
+      <c r="H23" s="15" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="4">
+      <c r="A24" s="9">
         <v>23</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="4">
+      <c r="D24" s="9">
         <v>80</v>
       </c>
-      <c r="E24" s="4">
+      <c r="E24" s="9">
         <v>840</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="10"/>
+      <c r="H24" s="15"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="11">
+      <c r="A25" s="16">
         <v>24</v>
       </c>
-      <c r="B25" s="12" t="s">
+      <c r="B25" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="12" t="s">
+      <c r="C25" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="16">
         <v>80</v>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="16">
         <v>920</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="13"/>
+      <c r="H25" s="18"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="2"/>
+      <c r="B27" s="7"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="1">
+      <c r="A28" s="6">
         <v>1</v>
       </c>
       <c r="B28" t="s">
@@ -2218,7 +2317,7 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="1">
+      <c r="A29" s="6">
         <v>2</v>
       </c>
       <c r="B29" t="s">
@@ -2226,7 +2325,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="1">
+      <c r="A30" s="6">
         <v>3</v>
       </c>
       <c r="B30" t="s">
@@ -2234,10 +2333,10 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="1">
+      <c r="A31" s="6">
         <v>4</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C31" t="s">
@@ -2248,10 +2347,10 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="1">
+      <c r="A32" s="6">
         <v>5</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
@@ -2262,10 +2361,10 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="1">
+      <c r="A33" s="6">
         <v>6</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="6" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
@@ -2276,10 +2375,10 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="1">
+      <c r="A34" s="6">
         <v>7</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="6" t="s">
         <v>54</v>
       </c>
       <c r="C34" t="s">
@@ -2290,10 +2389,10 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="1">
+      <c r="A35" s="6">
         <v>8</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="6" t="s">
         <v>57</v>
       </c>
       <c r="C35" t="s">
@@ -2304,10 +2403,10 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="2"/>
+      <c r="B37" s="7"/>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
@@ -2332,9 +2431,149 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6"/>
-  <sheetData/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="7.3" customWidth="1"/>
+    <col min="2" max="3" width="27.3" customWidth="1"/>
+    <col min="5" max="5" width="84.1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17.4" spans="1:5">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1"/>
+      <c r="B5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="5"/>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="5"/>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="1"/>
+      <c r="B8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="5"/>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="1"/>
+      <c r="B9" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="5"/>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="5"/>
+      <c r="D10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E10" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C11" s="5"/>
+      <c r="D11" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A7:A9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter alignWithMargins="0" scaleWithDoc="0"/>

--- a/功能需求.xlsx
+++ b/功能需求.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="98">
   <si>
     <t>一、需求数据</t>
   </si>
@@ -223,12 +223,18 @@
     <t>PLC给软件</t>
   </si>
   <si>
+    <t>备注</t>
+  </si>
+  <si>
     <t>软件准备好</t>
   </si>
   <si>
     <t>D622</t>
   </si>
   <si>
+    <t>软件状态</t>
+  </si>
+  <si>
     <t>软件给PLC的准备好(长度1个字，INT=1为准备好)</t>
   </si>
   <si>
@@ -238,6 +244,9 @@
     <t>D600</t>
   </si>
   <si>
+    <t>文件名</t>
+  </si>
+  <si>
     <t>PLC给软件的文件名（长度20个字，字符串（支持中文））</t>
   </si>
   <si>
@@ -253,6 +262,9 @@
     <t>D620</t>
   </si>
   <si>
+    <t>识图界限</t>
+  </si>
+  <si>
     <t>PLC给软件的识图界限(长度2个字，REAL)</t>
   </si>
   <si>
@@ -271,6 +283,9 @@
     <t>D623</t>
   </si>
   <si>
+    <t>识图结果</t>
+  </si>
+  <si>
     <t>软件给PLC的识图结果（成功或者失败）（长度1个字，INT =1成功 =2失败 =3未找到)</t>
   </si>
   <si>
@@ -280,13 +295,34 @@
     <t>D624</t>
   </si>
   <si>
+    <t>识图中</t>
+  </si>
+  <si>
     <t>软件给PLC的识图进行中(长度1个字，INT =1为进行中)</t>
   </si>
   <si>
+    <t>软件写状态</t>
+  </si>
+  <si>
     <t>D625</t>
   </si>
   <si>
+    <t>心跳</t>
+  </si>
+  <si>
     <t>软件状态 INT =1 存活PLC往里写0</t>
+  </si>
+  <si>
+    <t>给定新的任务号</t>
+  </si>
+  <si>
+    <t>D626</t>
+  </si>
+  <si>
+    <t>任务号</t>
+  </si>
+  <si>
+    <t>任务号，当变化时软件才开启自动识别</t>
   </si>
 </sst>
 </file>
@@ -463,12 +499,24 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -861,7 +909,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -885,16 +933,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -903,89 +951,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1002,6 +1050,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1765,551 +1819,551 @@
   <dimension ref="A1:H57"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="9.5" style="6" customWidth="1"/>
+    <col min="1" max="1" width="9.5" style="8" customWidth="1"/>
     <col min="2" max="2" width="21.5" customWidth="1"/>
     <col min="3" max="3" width="19.3" customWidth="1"/>
-    <col min="4" max="4" width="11.3" style="6" customWidth="1"/>
-    <col min="5" max="5" width="10" style="6" customWidth="1"/>
-    <col min="6" max="7" width="42.2" style="6" customWidth="1"/>
+    <col min="4" max="4" width="11.3" style="8" customWidth="1"/>
+    <col min="5" max="5" width="10" style="8" customWidth="1"/>
+    <col min="6" max="7" width="42.2" style="8" customWidth="1"/>
     <col min="8" max="8" width="19.8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
-    </row>
-    <row r="3" s="6" customFormat="1" ht="31.2" spans="1:8">
-      <c r="A3" s="8" t="s">
+      <c r="B1" s="9"/>
+    </row>
+    <row r="3" s="8" customFormat="1" ht="31.2" spans="1:8">
+      <c r="A3" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="A4" s="9">
+      <c r="A4" s="11">
         <v>1</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="11">
         <v>20</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="11">
         <v>0</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="13"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="15"/>
     </row>
     <row r="5" spans="1:8">
-      <c r="A5" s="9">
+      <c r="A5" s="11">
         <v>2</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="11">
         <v>1</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="11">
         <v>20</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="13"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="15"/>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="9">
+      <c r="A6" s="11">
         <v>3</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="11">
         <v>1</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="11">
         <v>21</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="9"/>
-      <c r="H6" s="13"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="15"/>
     </row>
     <row r="7" spans="1:8">
-      <c r="A7" s="9">
+      <c r="A7" s="11">
         <v>4</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="11">
         <v>1</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="11">
         <v>22</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="9"/>
-      <c r="H7" s="13"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="15"/>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="9">
+      <c r="A8" s="11">
         <v>5</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="11">
         <v>1</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="11">
         <v>23</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="13"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="15"/>
     </row>
     <row r="9" spans="1:8">
-      <c r="A9" s="9">
+      <c r="A9" s="11">
         <v>6</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="11">
         <v>1</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="11">
         <v>24</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="13"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="15"/>
     </row>
     <row r="10" spans="1:8">
-      <c r="A10" s="9">
+      <c r="A10" s="11">
         <v>7</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="11">
         <v>1</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="11">
         <v>25</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G10" s="9"/>
-      <c r="H10" s="13"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="15"/>
     </row>
     <row r="11" spans="1:8">
-      <c r="A11" s="9">
+      <c r="A11" s="11">
         <v>8</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="11">
         <v>26</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="9"/>
-      <c r="H11" s="13"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="15"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="9">
+      <c r="A12" s="11">
         <v>9</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="11">
         <v>1</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="11">
         <v>27</v>
       </c>
-      <c r="F12" s="9" t="s">
+      <c r="F12" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="13"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="15"/>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="9">
+      <c r="A13" s="11">
         <v>10</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="11">
         <v>1</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="11">
         <v>28</v>
       </c>
-      <c r="F13" s="9" t="s">
+      <c r="F13" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="13"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="15"/>
     </row>
     <row r="14" spans="1:8">
-      <c r="A14" s="9">
+      <c r="A14" s="11">
         <v>11</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="11">
         <v>1</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="11">
         <v>29</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="9"/>
-      <c r="H14" s="13"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="15"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="A15" s="9">
+      <c r="A15" s="11">
         <v>12</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="11">
         <v>2</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="11">
         <v>30</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="F15" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="9"/>
-      <c r="H15" s="13"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="15"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="9">
+      <c r="A16" s="11">
         <v>13</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="11">
         <v>2</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="11">
         <v>32</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="F16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="13"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="15"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="9">
+      <c r="A17" s="11">
         <v>14</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="11">
         <v>2</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="11">
         <v>32</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="13"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="15"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="9">
+      <c r="A18" s="11">
         <v>15</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="11">
         <v>2</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="11">
         <v>34</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G18" s="9"/>
-      <c r="H18" s="13"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="15"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="9">
+      <c r="A19" s="11">
         <v>16</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="11">
         <v>2</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="11">
         <v>38</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="G19" s="9"/>
-      <c r="H19" s="13"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="15"/>
     </row>
     <row r="20" ht="15" customHeight="1" spans="1:8">
-      <c r="A20" s="9">
+      <c r="A20" s="11">
         <v>17</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="11">
         <v>320</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="11">
         <v>40</v>
       </c>
-      <c r="F20" s="9" t="s">
+      <c r="F20" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="9"/>
-      <c r="H20" s="15" t="s">
+      <c r="G20" s="11"/>
+      <c r="H20" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:8">
-      <c r="A21" s="9">
+      <c r="A21" s="11">
         <v>19</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="11">
         <v>80</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="11">
         <v>360</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="F21" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H21" s="15"/>
+      <c r="H21" s="17"/>
     </row>
     <row r="22" spans="1:8">
-      <c r="A22" s="9">
+      <c r="A22" s="11">
         <v>20</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="11">
         <v>80</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="11">
         <v>440</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="F22" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H22" s="15"/>
+      <c r="H22" s="17"/>
     </row>
     <row r="23" ht="15" customHeight="1" spans="1:8">
-      <c r="A23" s="9">
+      <c r="A23" s="11">
         <v>21</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="11">
         <v>320</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="11">
         <v>520</v>
       </c>
-      <c r="F23" s="9" t="s">
+      <c r="F23" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G23" s="9"/>
-      <c r="H23" s="15" t="s">
+      <c r="G23" s="11"/>
+      <c r="H23" s="17" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:8">
-      <c r="A24" s="9">
+      <c r="A24" s="11">
         <v>23</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="11">
         <v>80</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="11">
         <v>840</v>
       </c>
-      <c r="F24" s="9" t="s">
+      <c r="F24" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H24" s="15"/>
+      <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8">
-      <c r="A25" s="16">
+      <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="17" t="s">
+      <c r="B25" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C25" s="17" t="s">
+      <c r="C25" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D25" s="18">
         <v>80</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="18">
         <v>920</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H25" s="18"/>
+      <c r="H25" s="20"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B27" s="7"/>
+      <c r="B27" s="9"/>
     </row>
     <row r="28" spans="1:8">
-      <c r="A28" s="6">
+      <c r="A28" s="8">
         <v>1</v>
       </c>
       <c r="B28" t="s">
@@ -2317,7 +2371,7 @@
       </c>
     </row>
     <row r="29" spans="1:8">
-      <c r="A29" s="6">
+      <c r="A29" s="8">
         <v>2</v>
       </c>
       <c r="B29" t="s">
@@ -2325,7 +2379,7 @@
       </c>
     </row>
     <row r="30" spans="1:8">
-      <c r="A30" s="6">
+      <c r="A30" s="8">
         <v>3</v>
       </c>
       <c r="B30" t="s">
@@ -2333,10 +2387,10 @@
       </c>
     </row>
     <row r="31" spans="1:8">
-      <c r="A31" s="6">
+      <c r="A31" s="8">
         <v>4</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C31" t="s">
@@ -2347,10 +2401,10 @@
       </c>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="6">
+      <c r="A32" s="8">
         <v>5</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C32" t="s">
@@ -2361,10 +2415,10 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6">
+      <c r="A33" s="8">
         <v>6</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C33" t="s">
@@ -2375,10 +2429,10 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="6">
+      <c r="A34" s="8">
         <v>7</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="8" t="s">
         <v>54</v>
       </c>
       <c r="C34" t="s">
@@ -2389,10 +2443,10 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="6">
+      <c r="A35" s="8">
         <v>8</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="8" t="s">
         <v>57</v>
       </c>
       <c r="C35" t="s">
@@ -2403,10 +2457,10 @@
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B37" s="7"/>
+      <c r="B37" s="9"/>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
@@ -2431,15 +2485,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="4"/>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="7.3" customWidth="1"/>
     <col min="2" max="3" width="27.3" customWidth="1"/>
-    <col min="5" max="5" width="84.1" customWidth="1"/>
+    <col min="5" max="5" width="16.6916666666667" customWidth="1"/>
+    <col min="6" max="6" width="84.1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.4" spans="1:5">
+    <row r="1" ht="17.4" spans="1:6">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>62</v>
@@ -2447,127 +2502,173 @@
       <c r="C1" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="E1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>67</v>
+      </c>
+      <c r="F2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>71</v>
+      </c>
+      <c r="F3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" s="5"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>4</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>77</v>
+      </c>
+      <c r="F6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" s="1"/>
       <c r="B8" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="1"/>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E10" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>88</v>
+      </c>
+      <c r="F11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>8</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="7"/>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>85</v>
+        <v>92</v>
+      </c>
+      <c r="F12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>9</v>
+      </c>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
